--- a/output/graficos_dimensiones/comunal_d_otras_relaciones_a_2021_los_lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_d_otras_relaciones_a_2021_los_lagos.xlsx
@@ -137,7 +137,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:31</t>
+    <t xml:space="preserve">2026-09-10 01:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_otras_relaciones_a_2021_los_lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_d_otras_relaciones_a_2021_los_lagos.xlsx
@@ -137,7 +137,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:47</t>
+    <t xml:space="preserve">2026-09-12 22:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_otras_relaciones_a_2021_los_lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_d_otras_relaciones_a_2021_los_lagos.xlsx
@@ -137,7 +137,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:58</t>
+    <t xml:space="preserve">2026-09-23 15:50</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_otras_relaciones_a_2021_los_lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_d_otras_relaciones_a_2021_los_lagos.xlsx
@@ -137,7 +137,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 15:50</t>
+    <t xml:space="preserve">2026-10-05 17:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
